--- a/GBU 2301/datasets/PelicanStores.xlsx
+++ b/GBU 2301/datasets/PelicanStores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e744a0cafea0a387/CBU/_Teaching/AUI/Business Statistics/GBU 2301/datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_7BBB9922403766A047F8A9B223EAAC35349EEE12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF68286B-4BBE-47A4-8606-E83B037EA14E}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_7BBB9922403766A047F8A9B223EAAC35349EEE12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D6EF479-F38D-42A2-9A3F-43D93CD9504C}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="8880" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="&amp;UnStack" sheetId="19" state="hidden" r:id="rId1"/>
@@ -24,7 +24,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Data!$A$1:$H$101</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -159,6 +172,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -517,7 +534,14 @@
   <dimension ref="A1:M101"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="8" width="9.59765625" customWidth="1"/>
+    <col min="1" max="1" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.8984375" customWidth="1"/>
     <col min="13" max="13" width="9" style="4" customWidth="1"/>
   </cols>
@@ -576,6 +600,7 @@
       <c r="H2" s="3">
         <v>32</v>
       </c>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
@@ -602,6 +627,7 @@
       <c r="H3" s="3">
         <v>36</v>
       </c>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
